--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -62891,7 +62891,7 @@
         <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>197389</v>
+        <v>197439</v>
       </c>
       <c r="C2719" t="n">
         <v>37.7000007629395</v>
@@ -62906,6 +62906,29 @@
         <v>36.8899993896484</v>
       </c>
       <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>116963</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>37.9249992370605</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>37.375</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>37.4099998474121</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>37.4900016784668</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -62914,7 +62914,7 @@
         <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>116963</v>
+        <v>117163</v>
       </c>
       <c r="C2720" t="n">
         <v>37.9249992370605</v>
@@ -62929,6 +62929,29 @@
         <v>37.4900016784668</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>170722</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>37.7200012207031</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>36.8549995422363</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>37.6199989318848</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>37</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -62937,7 +62937,7 @@
         <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>170722</v>
+        <v>170777</v>
       </c>
       <c r="C2721" t="n">
         <v>37.7200012207031</v>
@@ -62952,6 +62952,29 @@
         <v>37</v>
       </c>
       <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>193549</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>36.4000015258789</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>37.0250015258789</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>36.4099998474121</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -62960,7 +62960,7 @@
         <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>193549</v>
+        <v>193685</v>
       </c>
       <c r="C2722" t="n">
         <v>37.5</v>
@@ -62975,6 +62975,29 @@
         <v>36.4099998474121</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>115911</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>37.4900016784668</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>36.4300003051758</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>36.6599998474121</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>37.4599990844727</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>126731</v>
+        <v>71792</v>
       </c>
       <c r="C2716" t="n">
-        <v>39.875</v>
+        <v>40.0499992370605</v>
       </c>
       <c r="D2716" t="n">
-        <v>38.9700012207031</v>
+        <v>39.685001373291</v>
       </c>
       <c r="E2716" t="n">
-        <v>39.7700004577637</v>
+        <v>39.8300018310547</v>
       </c>
       <c r="F2716" t="n">
-        <v>38.9700012207031</v>
+        <v>39.8849983215332</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>102317</v>
+        <v>126731</v>
       </c>
       <c r="C2717" t="n">
+        <v>39.875</v>
+      </c>
+      <c r="D2717" t="n">
         <v>38.9700012207031</v>
       </c>
-      <c r="D2717" t="n">
-        <v>38.5299987792969</v>
-      </c>
       <c r="E2717" t="n">
-        <v>38.8300018310547</v>
+        <v>39.7700004577637</v>
       </c>
       <c r="F2717" t="n">
-        <v>38.6100006103516</v>
+        <v>38.9700012207031</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>86228</v>
+        <v>102317</v>
       </c>
       <c r="C2718" t="n">
-        <v>38.8450012207031</v>
+        <v>38.9700012207031</v>
       </c>
       <c r="D2718" t="n">
-        <v>38.2299995422363</v>
+        <v>38.5299987792969</v>
       </c>
       <c r="E2718" t="n">
-        <v>38.6150016784668</v>
+        <v>38.8300018310547</v>
       </c>
       <c r="F2718" t="n">
-        <v>38.2400016784668</v>
+        <v>38.6100006103516</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>197439</v>
+        <v>86228</v>
       </c>
       <c r="C2719" t="n">
-        <v>37.7000007629395</v>
+        <v>38.8450012207031</v>
       </c>
       <c r="D2719" t="n">
-        <v>36.8600006103516</v>
+        <v>38.2299995422363</v>
       </c>
       <c r="E2719" t="n">
-        <v>37.625</v>
+        <v>38.6150016784668</v>
       </c>
       <c r="F2719" t="n">
-        <v>36.8899993896484</v>
+        <v>38.2400016784668</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>117163</v>
+        <v>197439</v>
       </c>
       <c r="C2720" t="n">
-        <v>37.9249992370605</v>
+        <v>37.7000007629395</v>
       </c>
       <c r="D2720" t="n">
-        <v>37.375</v>
+        <v>36.8600006103516</v>
       </c>
       <c r="E2720" t="n">
-        <v>37.4099998474121</v>
+        <v>37.625</v>
       </c>
       <c r="F2720" t="n">
-        <v>37.4900016784668</v>
+        <v>36.8899993896484</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>170777</v>
+        <v>117163</v>
       </c>
       <c r="C2721" t="n">
-        <v>37.7200012207031</v>
+        <v>37.9249992370605</v>
       </c>
       <c r="D2721" t="n">
-        <v>36.8549995422363</v>
+        <v>37.375</v>
       </c>
       <c r="E2721" t="n">
-        <v>37.6199989318848</v>
+        <v>37.4099998474121</v>
       </c>
       <c r="F2721" t="n">
-        <v>37</v>
+        <v>37.4900016784668</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,22 +62957,22 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>193685</v>
+        <v>170777</v>
       </c>
       <c r="C2722" t="n">
-        <v>37.5</v>
+        <v>37.7200012207031</v>
       </c>
       <c r="D2722" t="n">
-        <v>36.4000015258789</v>
+        <v>36.8549995422363</v>
       </c>
       <c r="E2722" t="n">
-        <v>37.0250015258789</v>
+        <v>37.6199989318848</v>
       </c>
       <c r="F2722" t="n">
-        <v>36.4099998474121</v>
+        <v>37</v>
       </c>
       <c r="G2722" t="s">
         <v>7</v>
@@ -62980,24 +62980,47 @@
     </row>
     <row r="2723">
       <c r="A2723" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2723" t="n">
-        <v>115911</v>
+        <v>193685</v>
       </c>
       <c r="C2723" t="n">
-        <v>37.4900016784668</v>
+        <v>37.5</v>
       </c>
       <c r="D2723" t="n">
-        <v>36.4300003051758</v>
+        <v>36.4000015258789</v>
       </c>
       <c r="E2723" t="n">
-        <v>36.6599998474121</v>
+        <v>37.0250015258789</v>
       </c>
       <c r="F2723" t="n">
-        <v>37.4599990844727</v>
+        <v>36.4099998474121</v>
       </c>
       <c r="G2723" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2724" t="n">
+        <v>131158</v>
+      </c>
+      <c r="C2724" t="n">
+        <v>38.064998626709</v>
+      </c>
+      <c r="D2724" t="n">
+        <v>37.3699989318848</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>37.5999984741211</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>37.5699996948242</v>
+      </c>
+      <c r="G2724" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -63213,7 +63213,7 @@
         <v>46295.2916666667</v>
       </c>
       <c r="B2733" t="n">
-        <v>163647</v>
+        <v>163788</v>
       </c>
       <c r="C2733" t="n">
         <v>34.0999984741211</v>
@@ -63224,8 +63224,31 @@
       <c r="E2733" t="n">
         <v>33.4799995422363</v>
       </c>
-      <c r="F2733"/>
+      <c r="F2733" t="n">
+        <v>33.9850006103516</v>
+      </c>
       <c r="G2733" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2734" t="n">
+        <v>173328</v>
+      </c>
+      <c r="C2734" t="n">
+        <v>33.7599983215332</v>
+      </c>
+      <c r="D2734" t="n">
+        <v>33.1800003051758</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>33.5099983215332</v>
+      </c>
+      <c r="F2734"/>
+      <c r="G2734" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -63282,7 +63282,7 @@
         <v>46300.2916666667</v>
       </c>
       <c r="B2736" t="n">
-        <v>221644</v>
+        <v>222241</v>
       </c>
       <c r="C2736" t="n">
         <v>33.1450004577637</v>
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>32.8800010681152</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>32.9599990844727</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>141841</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>33.6049995422363</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>32.7200012207031</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>33.5849990844727</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -63305,7 +63305,7 @@
         <v>46301.2916666667</v>
       </c>
       <c r="B2737" t="n">
-        <v>141841</v>
+        <v>141907</v>
       </c>
       <c r="C2737" t="n">
         <v>33.6049995422363</v>
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>33.5849990844727</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>33.0499992370605</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>164933</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>34.189998626709</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>33.1199989318848</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>33.2750015258789</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -63328,7 +63328,7 @@
         <v>46302.2916666667</v>
       </c>
       <c r="B2738" t="n">
-        <v>164933</v>
+        <v>169262</v>
       </c>
       <c r="C2738" t="n">
         <v>34.189998626709</v>
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>33.2750015258789</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>34.189998626709</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>90270</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>33.9099998474121</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>33.4249992370605</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>33.9099998474121</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -63351,7 +63351,7 @@
         <v>46303.2916666667</v>
       </c>
       <c r="B2739" t="n">
-        <v>90270</v>
+        <v>93314</v>
       </c>
       <c r="C2739" t="n">
         <v>33.9099998474121</v>
@@ -63362,8 +63362,31 @@
       <c r="E2739" t="n">
         <v>33.9099998474121</v>
       </c>
-      <c r="F2739"/>
+      <c r="F2739" t="n">
+        <v>33.4599990844727</v>
+      </c>
       <c r="G2739" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>125471</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>34.4650001525879</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>33.7649993896484</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>33.8250007629395</v>
+      </c>
+      <c r="F2740"/>
+      <c r="G2740" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NOV.DE.xlsx
+++ b/data/NOV.DE.xlsx
@@ -63392,6 +63392,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2741">
+      <c r="A2741" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2741" t="n">
+        <v>84501</v>
+      </c>
+      <c r="C2741" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="D2741" t="n">
+        <v>34.2150001525879</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>34.4049987792969</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>34.4500007629395</v>
+      </c>
+      <c r="G2741" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
